--- a/docs/demo-materials/contract-sample-tests/合同样例-测试导入样本-正常-990行.xlsx
+++ b/docs/demo-materials/contract-sample-tests/合同样例-测试导入样本-正常-990行.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入样本" sheetId="1" r:id="Rb5c5c1082c054be3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="2" r:id="Ra386259505fd42d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入样本" sheetId="1" r:id="Rbb92b01c63114e66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="2" r:id="Rbdc2ec8f62514ad8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -98,8 +98,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="NormalImportNotes" displayName="NormalImportNotes" ref="A1:B4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:B4"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="NormalImportNotes" displayName="NormalImportNotes" ref="A1:B5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:B5"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="项目"/>
     <x:tableColumn id="2" name="内容"/>
@@ -7989,7 +7989,7 @@
     </x:row>
     <x:row r="961">
       <x:c r="A961" s="8" t="str">
-        <x:v>投资有风险。当您/贵机构认购或申购私募基金时，可能获得投资收益，但同时也面临着投资风险。您/贵机构在做出投资决策之前，请仔细阅读本风险揭示书和基金合同，充分认识本基金的风险收益特征和产品特性，认真考虑基金存在的各项风险因素，并充分考虑自身的风险承受能力，理性判断并谨慎做出投资决策。</x:v>
+        <x:v>投资有风险。当您/贵机构认购或申购私募基金时，可能获得投资收益，但同时也面临着投资风险。您/贵机构在做出投资决策之前，请仔细阅读本风险揭示书和基金合同，充分认识本基金的风险收益特征和产品特性，认真考虑基金存在的各项风险因素，并充分考虑自身的风险承受能力，理性判断并谨慎做出投资决策。（批量导入唯一性验证序号0960）</x:v>
       </x:c>
       <x:c r="B961" s="8" t="str">
         <x:v>25;28</x:v>
@@ -8005,7 +8005,7 @@
     </x:row>
     <x:row r="963">
       <x:c r="A963" s="8" t="str">
-        <x:v>（一）私募基金管理人保证在募集资金前已在中国证券投资基金业协会（以下简称中国基金业协会）登记为私募基金管理人，并取得管理人登记编码。</x:v>
+        <x:v>（一）私募基金管理人保证在募集资金前已在中国证券投资基金业协会（以下简称中国基金业协会）登记为私募基金管理人，并取得管理人登记编码。（批量导入唯一性验证序号0962）</x:v>
       </x:c>
       <x:c r="B963" s="8" t="str">
         <x:v>20;25;28;43;57</x:v>
@@ -8037,7 +8037,7 @@
     </x:row>
     <x:row r="967">
       <x:c r="A967" s="8" t="str">
-        <x:v>（五）私募基金管理人承诺遵循专业化运营的原则，在未经监管部门同意的情况下，不会从事私募投资基金以外的业务。</x:v>
+        <x:v>（五）私募基金管理人承诺遵循专业化运营的原则，在未经监管部门同意的情况下，不会从事私募投资基金以外的业务。（批量导入唯一性验证序号0966）</x:v>
       </x:c>
       <x:c r="B967" s="8" t="str">
         <x:v>32;33;34</x:v>
@@ -8053,7 +8053,7 @@
     </x:row>
     <x:row r="969">
       <x:c r="A969" s="8" t="str">
-        <x:v>（七）私募基金管理人承诺已和相关当事人在基金合同中约定私募基金管理人客观上丧失继续管理私募基金能力的情形下的基金财产安全保障、维持基金运营或清算的应急处置预案和纠纷解决机制，保证即使因违反法律法规或自律规则而被执行注销程序的私募基金管理人和相关当事人，能够根据《基金法》、协会相关自律规则和基金合同的约定，妥善处置基金财产，依法保障投资者的合法权益。</x:v>
+        <x:v>（七）私募基金管理人承诺已和相关当事人在基金合同中约定私募基金管理人客观上丧失继续管理私募基金能力的情形下的基金财产安全保障、维持基金运营或清算的应急处置预案和纠纷解决机制，保证即使因违反法律法规或自律规则而被执行注销程序的私募基金管理人和相关当事人，能够根据《基金法》、协会相关自律规则和基金合同的约定，妥善处置基金财产，依法保障投资者的合法权益。（批量导入唯一性验证序号0968）</x:v>
       </x:c>
       <x:c r="B969" s="8" t="str">
         <x:v>25</x:v>
@@ -8085,7 +8085,7 @@
     </x:row>
     <x:row r="973">
       <x:c r="A973" s="8" t="str">
-        <x:v>（三）基金募集机构与基金管理人存在关联关系的风险</x:v>
+        <x:v>（三）基金募集机构与基金管理人存在关联关系的风险（批量导入唯一性验证序号0972）</x:v>
       </x:c>
       <x:c r="B973" s="8" t="str">
         <x:v>20;25</x:v>
@@ -8101,7 +8101,7 @@
     </x:row>
     <x:row r="975">
       <x:c r="A975" s="8" t="str">
-        <x:v>基金管理人将其应负责的事项以服务外包方式委托其他机构办理，因受托机构不具备相关的提供服务的条件、或因管理不善、操作失误等，可能给投资者带来一定的风险。</x:v>
+        <x:v>基金管理人将其应负责的事项以服务外包方式委托其他机构办理，因受托机构不具备相关的提供服务的条件、或因管理不善、操作失误等，可能给投资者带来一定的风险。（批量导入唯一性验证序号0974）</x:v>
       </x:c>
       <x:c r="B975" s="8" t="str">
         <x:v>25;28</x:v>
@@ -8133,7 +8133,7 @@
     </x:row>
     <x:row r="979">
       <x:c r="A979" s="8" t="str">
-        <x:v>如果在基金成立后不能及时完成备案，将可能导致本基金错过市场行情或投资机会；如果本基金在成立后无法获得基金业协会的备案或不予备案，则将直接影响本基金设立目的的实现。当出现无法通过基金业协会备案或不予备案的情形，本基金按照本合同约定提前终止并进行清算，由此直接影响投资者参与本基金的投资目的。</x:v>
+        <x:v>如果在基金成立后不能及时完成备案，将可能导致本基金错过市场行情或投资机会；如果本基金在成立后无法获得基金业协会的备案或不予备案，则将直接影响本基金设立目的的实现。当出现无法通过基金业协会备案或不予备案的情形，本基金按照本合同约定提前终止并进行清算，由此直接影响投资者参与本基金的投资目的。（批量导入唯一性验证序号0978）</x:v>
       </x:c>
       <x:c r="B979" s="8" t="str">
         <x:v>26;54;76</x:v>
@@ -8149,7 +8149,7 @@
     </x:row>
     <x:row r="981">
       <x:c r="A981" s="8" t="str">
-        <x:v>证券及期货等经纪服务商由管理人自行聘任，经纪服务商的服务水平和服务能力由管理人自行审核并承担相应责任。管理人委托的经纪服务商应向托管人提供基金参与证券、期货等交易的相关数据及凭证。若因管理人、经纪服务商或交易所、登记公司、股转系统等原因导致托管人未能及时、完整、准确获得交易数据或凭证，影响托管人履行投资监督、估值核算、账目核对等职责的，可能存在造成委托人财产损失的风险。</x:v>
+        <x:v>证券及期货等经纪服务商由管理人自行聘任，经纪服务商的服务水平和服务能力由管理人自行审核并承担相应责任。管理人委托的经纪服务商应向托管人提供基金参与证券、期货等交易的相关数据及凭证。若因管理人、经纪服务商或交易所、登记公司、股转系统等原因导致托管人未能及时、完整、准确获得交易数据或凭证，影响托管人履行投资监督、估值核算、账目核对等职责的，可能存在造成委托人财产损失的风险。（批量导入唯一性验证序号0980）</x:v>
       </x:c>
       <x:c r="B981" s="8" t="str">
         <x:v>32;33;34</x:v>
@@ -8181,7 +8181,7 @@
     </x:row>
     <x:row r="985">
       <x:c r="A985" s="8" t="str">
-        <x:v>本基金设置了平仓机制，但该机制并非对平仓结果的保证。管理人因私募基金交易结算模式和/或持仓品种跌停、停牌、无法交易等原因无法在跌破或触及平仓线后第一个交易日进行平仓操作，且因市场原因持仓品种价格可能持续向不利方向变动，持仓品种也可能无法及时平仓，存在本基金在执行平仓操作后的基金份额净值可能低于平仓线的风险。此外，如管理人未按照基金合同的约定及时启动和执行平仓机制，也可能导致实际平仓后的基金份额净值低于平仓线的风险。</x:v>
+        <x:v>本基金设置了平仓机制，但该机制并非对平仓结果的保证。管理人因私募基金交易结算模式和/或持仓品种跌停、停牌、无法交易等原因无法在跌破或触及平仓线后第一个交易日进行平仓操作，且因市场原因持仓品种价格可能持续向不利方向变动，持仓品种也可能无法及时平仓，存在本基金在执行平仓操作后的基金份额净值可能低于平仓线的风险。此外，如管理人未按照基金合同的约定及时启动和执行平仓机制，也可能导致实际平仓后的基金份额净值低于平仓线的风险。（批量导入唯一性验证序号0984）</x:v>
       </x:c>
       <x:c r="B985" s="8" t="str">
         <x:v>43</x:v>
@@ -8197,7 +8197,7 @@
     </x:row>
     <x:row r="987">
       <x:c r="A987" s="8" t="str">
-        <x:v>该等分配方式可能出现基金收益分配时基金资产无法及时变现导致托管账户中现金不足以足额支付分红款项或收益分配后基金份额净值大幅度变化等风险，前述由于分配未实现收益导致的风险由管理人负责控制。6、单一投资标的的投资风险 本基金主要投资单一标的基金，本基金的风险收益情况由单一标的基金的投资情况决定，本基金面临的风险包括但不限于标的基金的管理人的经营风险和标的基金运作风险，其中标的基金的管理人的经营风险指本基金所投资的标的基金的管理人经营不善，造成本基金投资收益下降；标的基金运作风险包括标的基金投资决策失误、投资经理更换、运营差错、存续期届满或由于其他原因而清盘等导致的风险。</x:v>
+        <x:v>该等分配方式可能出现基金收益分配时基金资产无法及时变现导致托管账户中现金不足以足额支付分红款项或收益分配后基金份额净值大幅度变化等风险，前述由于分配未实现收益导致的风险由管理人负责控制。6、单一投资标的的投资风险 本基金主要投资单一标的基金，本基金的风险收益情况由单一标的基金的投资情况决定，本基金面临的风险包括但不限于标的基金的管理人的经营风险和标的基金运作风险，其中标的基金的管理人的经营风险指本基金所投资的标的基金的管理人经营不善，造成本基金投资收益下降；标的基金运作风险包括标的基金投资决策失误、投资经理更换、运营差错、存续期届满或由于其他原因而清盘等导致的风险。（批量导入唯一性验证序号0986）</x:v>
       </x:c>
       <x:c r="B987" s="8" t="str">
         <x:v>20;25</x:v>
@@ -8229,7 +8229,7 @@
     </x:row>
     <x:row r="991">
       <x:c r="A991" s="8" t="str">
-        <x:v>上述关于本基金的风险等级由募集机构评定。</x:v>
+        <x:v>上述关于本基金的风险等级由募集机构评定。（批量导入唯一性验证序号0990）</x:v>
       </x:c>
       <x:c r="B991" s="8" t="str">
         <x:v>20;25;28;43;57</x:v>
@@ -8238,7 +8238,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra81fc1c455a04237"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R962d4b2b4f7b4d9b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8264,7 +8264,7 @@
         <x:v>用途</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>用于正常导入演示，覆盖单标签、多标签、合同原文段落和轻微改写段落。</x:v>
+        <x:v>用于接近单Excel 1000行限制的成功导入、同步Embedding和索引刷新验证。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -8272,21 +8272,29 @@
         <x:v>数据来源</x:v>
       </x:c>
       <x:c r="B3" s="8" t="str">
-        <x:v>从样例合同抽取 958 条可用段落，并生成同主题改写样本。</x:v>
+        <x:v>从样例合同抽取 958 条可用段落，并补充唯一性验证改写样本。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="8" t="str">
-        <x:v>注意</x:v>
+        <x:v>结构检查</x:v>
       </x:c>
       <x:c r="B4" s="8" t="str">
-        <x:v>编码为演示标签，不代表真实业务人工标注结果。</x:v>
+        <x:v>990条段落文本唯一，不包含同段落不同编码冲突。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="8" t="str">
+        <x:v>重要限制</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="str">
+        <x:v>编码为规则验证标签，不代表真实业务人工标注结果；不要用于预测准确性判断。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9fcaa21c1454bbf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R532f15c140c7421d"/>
   </x:tableParts>
 </x:worksheet>
 </file>